--- a/Statistical_documentation_in_R/main_results/compact_descriptives.xlsx
+++ b/Statistical_documentation_in_R/main_results/compact_descriptives.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">GDPpc</t>
   </si>
   <si>
-    <t xml:space="preserve">Pop15_65</t>
+    <t xml:space="preserve">Pop15_64</t>
   </si>
   <si>
     <t xml:space="preserve">YouthUnempl</t>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">c_log_GDPpc</t>
   </si>
   <si>
-    <t xml:space="preserve">c_log_Pop15_65</t>
+    <t xml:space="preserve">c_log_Pop15_64</t>
   </si>
   <si>
     <t xml:space="preserve">c_YouthUnempl</t>
@@ -504,7 +504,7 @@
         <v>36355</v>
       </c>
       <c r="L2" t="n">
-        <v>6.26346220473797</v>
+        <v>6.26346220473798</v>
       </c>
       <c r="M2" t="n">
         <v>45.2209110227492</v>
@@ -551,10 +551,10 @@
         <v>0.344875141310522</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0437425328523644</v>
+        <v>-0.0437425328523688</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0546557992249565</v>
+        <v>0.0546557992249566</v>
       </c>
     </row>
     <row r="4">
@@ -712,7 +712,7 @@
         <v>0.888767525149355</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00000000659958872690769</v>
+        <v>0.00000000659958897381019</v>
       </c>
       <c r="I7" t="n">
         <v>0.0000000000665008889080121</v>
@@ -724,7 +724,7 @@
         <v>4.17770077036441</v>
       </c>
       <c r="L7" t="n">
-        <v>1.86703500758942</v>
+        <v>1.86703500758943</v>
       </c>
       <c r="M7" t="n">
         <v>4.95930004701561</v>
@@ -808,7 +808,7 @@
         <v>715</v>
       </c>
       <c r="G2" t="n">
-        <v>1078.60372340426</v>
+        <v>1078.60372340425</v>
       </c>
       <c r="H2" t="n">
         <v>756.126</v>
@@ -823,7 +823,7 @@
         <v>33625</v>
       </c>
       <c r="L2" t="n">
-        <v>6.17386321050042</v>
+        <v>6.17386321050041</v>
       </c>
       <c r="M2" t="n">
         <v>44.5420456325636</v>
@@ -867,10 +867,10 @@
         <v>6.86871740625538</v>
       </c>
       <c r="L3" t="n">
-        <v>0.323058706207773</v>
+        <v>0.323058706207772</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.136377959038168</v>
+        <v>-0.136377959038177</v>
       </c>
       <c r="N3" t="n">
         <v>0.0569966639533421</v>
@@ -934,13 +934,13 @@
         <v>0.444444444444444</v>
       </c>
       <c r="E5" t="n">
-        <v>0.497435727624003</v>
+        <v>0.497435727624004</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.430851063829787</v>
+        <v>0.430851063829789</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2228904922785</v>
+        <v>0.222890492278497</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.954482385492</v>
+        <v>-1.95448238549201</v>
       </c>
       <c r="N5" t="n">
         <v>0.0229939746435395</v>
@@ -975,16 +975,16 @@
         <v>468</v>
       </c>
       <c r="D6" t="n">
-        <v>0.222222222222222</v>
+        <v>0.222222222222223</v>
       </c>
       <c r="E6" t="n">
-        <v>0.416184589072896</v>
+        <v>0.416184589072894</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.154255319148936</v>
+        <v>0.154255319148935</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -999,13 +999,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33202546559945</v>
+        <v>1.33202546559944</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.226177757427756</v>
+        <v>-0.226177757427696</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0192381394353876</v>
+        <v>0.0192381394353875</v>
       </c>
     </row>
     <row r="7">
@@ -1072,10 +1072,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.888914303480087</v>
+        <v>0.888914303480088</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00000000659958872690769</v>
+        <v>0.00000000659958897381019</v>
       </c>
       <c r="I8" t="n">
         <v>0.0000000000665008889080121</v>
@@ -1090,7 +1090,7 @@
         <v>1.86643547802068</v>
       </c>
       <c r="M8" t="n">
-        <v>4.95589244776234</v>
+        <v>4.95589244776233</v>
       </c>
       <c r="N8" t="n">
         <v>0.0356226022015573</v>
@@ -1107,10 +1107,10 @@
         <v>468</v>
       </c>
       <c r="D9" t="n">
-        <v>46483.3602444388</v>
+        <v>46481.3660381034</v>
       </c>
       <c r="E9" t="n">
-        <v>26863.7665441484</v>
+        <v>26866.4108251434</v>
       </c>
       <c r="F9" t="n">
         <v>43093.4547322872</v>
@@ -1131,13 +1131,13 @@
         <v>134228.596209342</v>
       </c>
       <c r="L9" t="n">
-        <v>0.931538604621918</v>
+        <v>0.931095923796639</v>
       </c>
       <c r="M9" t="n">
-        <v>1.24907295502892</v>
+        <v>1.24836463596358</v>
       </c>
       <c r="N9" t="n">
-        <v>1241.77804778232</v>
+        <v>1241.90027971455</v>
       </c>
     </row>
     <row r="10">
@@ -1151,7 +1151,7 @@
         <v>468</v>
       </c>
       <c r="D10" t="n">
-        <v>42599339.258547</v>
+        <v>42599339.2585471</v>
       </c>
       <c r="E10" t="n">
         <v>138073627.776089</v>
@@ -1160,7 +1160,7 @@
         <v>6552301.5</v>
       </c>
       <c r="G10" t="n">
-        <v>15306070.4734043</v>
+        <v>15306070.4734042</v>
       </c>
       <c r="H10" t="n">
         <v>8121730.2432</v>
@@ -1198,7 +1198,7 @@
         <v>15.315405982906</v>
       </c>
       <c r="E11" t="n">
-        <v>8.43441038848717</v>
+        <v>8.43441038848716</v>
       </c>
       <c r="F11" t="n">
         <v>13.563</v>
@@ -1266,7 +1266,7 @@
         <v>0.144084051441243</v>
       </c>
       <c r="M12" t="n">
-        <v>0.847676944035528</v>
+        <v>0.847676944035529</v>
       </c>
       <c r="N12" t="n">
         <v>0.0798648059469386</v>
@@ -1283,37 +1283,37 @@
         <v>468</v>
       </c>
       <c r="D13" t="n">
-        <v>0.000000000000000690521732184397</v>
+        <v>0.000000000000000413131067817246</v>
       </c>
       <c r="E13" t="n">
-        <v>0.780297320686189</v>
+        <v>0.780584476132717</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1465471760777</v>
+        <v>0.146729641566239</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0972655537434844</v>
+        <v>0.0974480192320235</v>
       </c>
       <c r="H13" t="n">
         <v>0.502815918625725</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.68314617262947</v>
+        <v>-2.68296370714093</v>
       </c>
       <c r="J13" t="n">
-        <v>1.301494661727</v>
+        <v>1.30167712721554</v>
       </c>
       <c r="K13" t="n">
         <v>3.98464083435647</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.46551192038271</v>
+        <v>-1.4649251108097</v>
       </c>
       <c r="M13" t="n">
-        <v>2.59250325176112</v>
+        <v>2.5865327440193</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0360692564082208</v>
+        <v>0.0360825301734321</v>
       </c>
     </row>
     <row r="14">
@@ -1327,16 +1327,16 @@
         <v>468</v>
       </c>
       <c r="D14" t="n">
-        <v>0.000000000000000523531112366237</v>
+        <v>0.000000000000000235329324877811</v>
       </c>
       <c r="E14" t="n">
-        <v>1.73130792212002</v>
+        <v>1.73130792212003</v>
       </c>
       <c r="F14" t="n">
         <v>-0.216558288526471</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.053787718458122</v>
+        <v>-0.0537877184581227</v>
       </c>
       <c r="H14" t="n">
         <v>1.89544146514036</v>
@@ -1354,10 +1354,10 @@
         <v>0.352056220175677</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.175985992480599</v>
+        <v>-0.175985992480605</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0800297370105226</v>
+        <v>0.0800297370105227</v>
       </c>
     </row>
     <row r="15">
@@ -1371,10 +1371,10 @@
         <v>468</v>
       </c>
       <c r="D15" t="n">
-        <v>0.000000000000000377000262086297</v>
+        <v>0.0000000000000000759126854444551</v>
       </c>
       <c r="E15" t="n">
-        <v>8.43441038848717</v>
+        <v>8.43441038848716</v>
       </c>
       <c r="F15" t="n">
         <v>-1.75240598290598</v>
